--- a/Etapa Construcción - Iteración 2/Diseño - Especificación de CUs ／ Casos de prueba/Casos de prueba 2° tanda de Casos de Uso- Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 2/Diseño - Especificación de CUs ／ Casos de prueba/Casos de prueba 2° tanda de Casos de Uso- Kairos - NexTech.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="302">
-  <si>
-    <t>Casos de Prueba CU 07: Crear Etapa</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="365">
+  <si>
+    <t>Casos de Prueba CU 07: Crear etapa</t>
   </si>
   <si>
     <t>Condición</t>
@@ -133,9 +133,6 @@
     <t>Baja</t>
   </si>
   <si>
-    <t>Campos obligatorios</t>
-  </si>
-  <si>
     <t>CP07_02_V1</t>
   </si>
   <si>
@@ -208,8 +205,10 @@
     <t>CP07_03_V3</t>
   </si>
   <si>
-    <t>Nombre: "Inicio", Descripción: "El amanecer iluminaba el valle con tonos dorados mientras el viento suave movía las hojas. Los pájaros cantaban entre los árboles y el aroma de la tierra húmeda anunciaba un nuevo día lleno de promesas, calma y esperanza para todos los que despertaban en aquel rincón tranquilo.
-", Fecha Inicio: 09/09/2025, Fecha de fin: 19/08/2025</t>
+    <t>Variante 3</t>
+  </si>
+  <si>
+    <t>Nombre: "Inicio", Descripción: "El amanecer iluminaba el valle con tonos dorados mientras el viento suave movía las hojas. Los pájaros cantaban entre los árboles y el aroma de la tierra húmeda anunciaba un nuevo día lleno de promesas, calma y esperanza para todos los que despeaaaaaaaaaac", Fecha Inicio: 09/09/2025, Fecha de fin: 19/08/2025</t>
   </si>
   <si>
     <t>1. Iniciar sesión como Líder de Proyecto. 
@@ -224,10 +223,28 @@
     <t>El sistema no crea la etapa y muestra el mensaje "No se pudo crear la etapa"</t>
   </si>
   <si>
+    <t>CP07_03_V4</t>
+  </si>
+  <si>
+    <t>Variante 4</t>
+  </si>
+  <si>
+    <t>Nombre: "Inicio", Descripción: "El amanecer iluminaba el valle con tonos dorados mientras el viento suave movía las hojas. Los pájaros cantaban entre los árboles y el aroma de la tierra húmeda anunciaba un nuevo día lleno de promesas, calma y esperanza para todos los que despeaaaaaaaaaa", Fecha Inicio: 09/09/2025, Fecha de fin: 19/08/2025</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesión como Líder de Proyecto. 
+2. Acceder a la sección "Etapas". 
+3. Presionar el botón “Crear etapa”. 
+4. Completar los campos obligatoiros y agregar una descripción de 255 caracteres.</t>
+  </si>
+  <si>
+    <t>El sistema crea la etapa y se actualiza el listado de etapas.</t>
+  </si>
+  <si>
+    <t>Resultado esperado.</t>
+  </si>
+  <si>
     <t>CP07_04_V1</t>
-  </si>
-  <si>
-    <t>Variante 3</t>
   </si>
   <si>
     <t>No se ingresan datos.</t>
@@ -243,9 +260,6 @@
 El sistema elimina la etapa. Al volver a ingresar, la etapa se mantiene eliminada.</t>
   </si>
   <si>
-    <t>Resultado esperado.</t>
-  </si>
-  <si>
     <t>CP07_05_V1</t>
   </si>
   <si>
@@ -261,6 +275,9 @@
     <t>El sistema crea otra etapa igual a una ya existente.</t>
   </si>
   <si>
+    <t>Casos de Prueba CU 08: Crear iteración</t>
+  </si>
+  <si>
     <t>Módulo de Iteraciones</t>
   </si>
   <si>
@@ -292,9 +309,6 @@
     <t>La iteración se crea correctamente y se muestra en la lista de iteraciones.</t>
   </si>
   <si>
-    <t>Campo obligatorio</t>
-  </si>
-  <si>
     <t>CP08_02_V1</t>
   </si>
   <si>
@@ -312,6 +326,9 @@
     <t>Se muestra el mensaje “Debe ingresar una descripción”.</t>
   </si>
   <si>
+    <t>El formulario no deja enviar con campos vacios</t>
+  </si>
+  <si>
     <t>CP08_02_V2</t>
   </si>
   <si>
@@ -325,7 +342,10 @@
     <t>Se muestra “Debe ingresar una fecha de inicio válida”.</t>
   </si>
   <si>
-    <t>Consistencia de datos</t>
+    <t>No se obtuvo el resultado esperado</t>
+  </si>
+  <si>
+    <t>El sistema permite guardar aunque la fecha no sea válida, ej aa/bb/2025</t>
   </si>
   <si>
     <t>CP08_03_V1</t>
@@ -344,6 +364,9 @@
     <t>Se muestra el mensaje “La fecha de fin no puede ser anterior a la fecha de inicio”.</t>
   </si>
   <si>
+    <t>El sistema guarda las fechas aunque esta sea anterior a la fecha de inicio</t>
+  </si>
+  <si>
     <t>CP08_03_V2</t>
   </si>
   <si>
@@ -360,7 +383,7 @@
     <t>Se muestra “Las fechas se superponen con otra iteración existente”.</t>
   </si>
   <si>
-    <t>Número de iteración</t>
+    <t>El sistema guarda la fechas superpuestas</t>
   </si>
   <si>
     <t>CP08_04_V1</t>
@@ -379,7 +402,7 @@
     <t>Se muestra el mensaje “Número de iteración inválido”.</t>
   </si>
   <si>
-    <t>Cancelación</t>
+    <t>El formulario deja enviar números negativos</t>
   </si>
   <si>
     <t>CP08_05_V1</t>
@@ -422,31 +445,152 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Casos de Prueba CU 13: Asignar Dependencia</t>
+  </si>
+  <si>
     <t>Módulo de tareas</t>
   </si>
   <si>
-    <t>CU13_1</t>
+    <t>CP13_01_V1</t>
   </si>
   <si>
     <t>Variación 1</t>
   </si>
   <si>
+    <t>Tarea 1 (fecha inicio: 05/10/2025, fecha fin: 07/10/2025, iteración 1, sin dependencias previas)
+Tarea 2 (fecha inicio: 08/10/2025, fecha fin: 10/10/2025, iteración 1, sin dependencias previas)</t>
+  </si>
+  <si>
+    <t>1: Inciar sesión.
+2: Ir a "planificación".
+3. Seleccionar la tarea 2  y presionar "Editar". 
+4. Asignarle dependencia de la Tarea 1
+5. Presionar "Aceptar"</t>
+  </si>
+  <si>
+    <t>El sistema registra la dependencia.</t>
+  </si>
+  <si>
+    <t>Lider del proyecto</t>
+  </si>
+  <si>
+    <t>CP13_02_V1</t>
+  </si>
+  <si>
+    <t>Variación 2</t>
+  </si>
+  <si>
+    <t>1: Inciar sesión.
+2: Ir a "planificación".
+3. Seleccionar la tarea 1  y presionar "Editar". 
+4. Asignarle dependencia de la Tarea 2
+5. Presionar "Aceptar"</t>
+  </si>
+  <si>
+    <t>El sistema no registra la dependencia y muestra una advertencia indicando error de dependencia debido a las fechas.</t>
+  </si>
+  <si>
+    <t>CP13_03_V1</t>
+  </si>
+  <si>
+    <t>Variación 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarea 1 (fecha inicio: 05/10/2025, fecha fin: 07/10/2025, iteración 1, sin dependencias previas)
+</t>
+  </si>
+  <si>
+    <t>1: Inciar sesión.
+2: Ir a "planificación".
+3. Seleccionar la tarea 1  y presionar "Editar". 
+4. Asignarle dependencia de la Tarea 1.
+5. Presionar "Aceptar"</t>
+  </si>
+  <si>
+    <t>El sistema no registra la dependencia y muestra una advertencia indicando error de dependencia debido a dependencias circulares.</t>
+  </si>
+  <si>
+    <t>CP13_04_V1</t>
+  </si>
+  <si>
+    <t>Variacion 4</t>
+  </si>
+  <si>
+    <t>Tarea 1 (fecha inicio: 05/10/2025, fecha fin: 07/10/2025, iteración 1, sin dependencias previas)
+Tarea 2 (fecha inicio: 08/10/2025, fecha fin: 10/10/2025, iteración 1, dependencia de Tarea 1)</t>
+  </si>
+  <si>
+    <t>1: Inciar sesión.
+2: Ir a "planificación".
+3. Seleccionar la tarea 1  y presionar "Editar". 
+4. Asignarle dependencia de la Tarea 2.
+5. Presionar "Aceptar"</t>
+  </si>
+  <si>
+    <t>El sistema registra las dependencia.</t>
+  </si>
+  <si>
+    <t>CP13_05_V1</t>
+  </si>
+  <si>
+    <t>Variacion 5</t>
+  </si>
+  <si>
+    <t>Tarea 1 (fecha inicio: 05/10/2025, fecha fin: 07/10/2025, iteración 1, sin dependencias previas)
+Tarea 3 (fecha inicio: 08/11/2025, fecha fin: 10/11/2025, iteración 2, sin dependencias previas)</t>
+  </si>
+  <si>
+    <t>1: Inciar sesión.
+2: Ir a "planificación".
+3. Seleccionar la tarea 1  y presionar "Editar". 
+4. Asignarle dependencia de la Tarea 3.
+5. Presionar "Aceptar"</t>
+  </si>
+  <si>
+    <t>El sistema no registra la dependencia y muestra una advertencia indicando error de dependencia debido a que las tareas deben formar parte de la misma iteración.</t>
+  </si>
+  <si>
+    <t>CP13_06_V1</t>
+  </si>
+  <si>
+    <t>Variacion 6</t>
+  </si>
+  <si>
+    <t>1: Inciar sesión.
+2: Ir a "planificación".
+3. Seleccionar la tarea 2  y presionar "Editar". 
+4. Asignarle dependencia de ninguna tarea.
+5. Presionar "Aceptar"</t>
+  </si>
+  <si>
+    <t>El sistema actualiza las dependencias y la Tarea 2 queda sin dependencias.</t>
+  </si>
+  <si>
+    <t>Casos de Prueba CU 14: Modificar estado de tarea</t>
+  </si>
+  <si>
+    <t>CU14_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tarea: Crear cierre iteración </t>
   </si>
   <si>
     <t>1: Inciar sesión.
-2: Ir a "planificación"
-3: Seleccionar "Crear cierre de iteración"
-4: Elegir la opción "Completada"</t>
-  </si>
-  <si>
-    <t>Lider del proyecto</t>
+2: Ir a "planificación".
+3: Seleccionar la tarea "Crear cierre de iteración".
+4: Elegir la opción "Completada".</t>
+  </si>
+  <si>
+    <t>El estado cambia a “Completado” y se actualiza el campo.</t>
+  </si>
+  <si>
+    <t>Se obtuvo el resultado esperado</t>
+  </si>
+  <si>
+    <t>Gonzalo Ulloa</t>
   </si>
   <si>
     <t>CU14_2</t>
-  </si>
-  <si>
-    <t>Variación 2</t>
   </si>
   <si>
     <t>1: Iniciar sesión. 
@@ -455,10 +599,19 @@
 4: Elegir la opción "En progeso"</t>
   </si>
   <si>
+    <t>El estado cambia a “En progreso” y se actualiza el campo.</t>
+  </si>
+  <si>
     <t>CU14_3</t>
   </si>
   <si>
-    <t>Variación 3</t>
+    <t>1: Iniciar sesión. 
+2: Ir a "planificación".
+3: Seleccionar "Crear cierre de iteración".
+4: Elegir la opción "En progeso".</t>
+  </si>
+  <si>
+    <t>El estado se persiste en la base de datos.</t>
   </si>
   <si>
     <t>CU14_4</t>
@@ -467,51 +620,27 @@
     <t>Vista del usuario</t>
   </si>
   <si>
-    <t>Variacion 4</t>
-  </si>
-  <si>
     <t>Panel lateral: Progreso general</t>
   </si>
   <si>
     <t>1: Inciar sesión.
-2: Ir a "planificación"
-3: Cambiar estado de tareas a "Completo"</t>
-  </si>
-  <si>
-    <t>CU14_1</t>
-  </si>
-  <si>
-    <t>El estado cambia a “Completado” y se actualiza el campo .</t>
-  </si>
-  <si>
-    <t>Se obtuvo el resultado esperado</t>
-  </si>
-  <si>
-    <t>Gonzalo Ulloa</t>
-  </si>
-  <si>
-    <t>El estado cambia a “En progreso” y se actualiza el campo .</t>
-  </si>
-  <si>
-    <t>El estado se persiste en la base de datos</t>
-  </si>
-  <si>
-    <t>La barra del "Progreso general" debe aumentar</t>
+2: Ir a "planificación".
+3: Cambiar estado de tareas a "Completo".</t>
+  </si>
+  <si>
+    <t>La barra del "Progreso general" debe aumentar.</t>
   </si>
   <si>
     <t>CU14_5</t>
   </si>
   <si>
-    <t>Variacion 5</t>
-  </si>
-  <si>
     <t>1: Inciar sesión.
-2: Ir a "planificación"
-3: Comentar una tarea
-4: Cambiar el estado de la tarea a "Completo"</t>
-  </si>
-  <si>
-    <t>La tarea cambia su estado a "Completo"</t>
+2: Ir a "planificación".
+3: Comentar una tarea.
+4: Cambiar el estado de la tarea a "Completo".</t>
+  </si>
+  <si>
+    <t>La tarea cambia su estado a "Completo".</t>
   </si>
   <si>
     <t>CU14_6</t>
@@ -521,12 +650,12 @@
   </si>
   <si>
     <t>1: Inciar sesión.
-2: Ir a "planificación"
-3: Comentar una tarea
-4: Cambiar el estado de la tarea a "En progeso"</t>
-  </si>
-  <si>
-    <t>La tarea cambia su estado a "En progreso"</t>
+2: Ir a "planificación".
+3: Comentar una tarea.
+4: Cambiar el estado de la tarea a "En progeso".</t>
+  </si>
+  <si>
+    <t>La tarea cambia su estado a "En progreso".</t>
   </si>
   <si>
     <t>CU14_7</t>
@@ -536,13 +665,13 @@
   </si>
   <si>
     <t>1: Inciar sesión.
-2: Ir a "planificación"
-3: Comentar una tarea
-4: Asignar dependencia
-4: Cambiar el estado de la tarea a "Completar"</t>
-  </si>
-  <si>
-    <t>La tarea cambia su estado a "Completado"</t>
+2: Ir a "planificación".
+3: Comentar una tarea.
+4: Asignar dependencia.
+4: Cambiar el estado de la tarea a "Completar".</t>
+  </si>
+  <si>
+    <t>La tarea cambia su estado a "Completado".</t>
   </si>
   <si>
     <t>CU14_8</t>
@@ -552,10 +681,10 @@
   </si>
   <si>
     <t>1: Inciar sesión.
-2: Ir a "planificación"
-3: Comentar una tarea
-4: Asignar dependencia
-4: Cambiar el estado de la tarea a "En progreso"</t>
+2: Ir a "planificación".
+3: Comentar una tarea.
+4: Asignar dependencia.
+4: Cambiar el estado de la tarea a "En progreso".</t>
   </si>
   <si>
     <t>Seguridad</t>
@@ -567,14 +696,14 @@
     <t>Variacion 1</t>
   </si>
   <si>
-    <t xml:space="preserve">1: Accede a la vista sin iniciar sesion
-2: Cambiar estado "Completar" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La tarea rechaza el cambio </t>
-  </si>
-  <si>
-    <t>No se obtuvo el resultado esperado</t>
+    <t>1: Accede a la vista sin iniciar sesión
+2: Cambiar estado "Completar".</t>
+  </si>
+  <si>
+    <t>La tarea rechaza el cambio .</t>
+  </si>
+  <si>
+    <t>Casos de Prueba CU 15: Visualizar tarea</t>
   </si>
   <si>
     <t>Módulo de Tareas</t>
@@ -603,24 +732,44 @@
     <t>Líder de Proyecto / Miembro</t>
   </si>
   <si>
-    <t>CP15_2</t>
+    <t>Florencia Mendez</t>
+  </si>
+  <si>
+    <t>CP15_2_V1</t>
   </si>
   <si>
     <t>Ordenar listado de tareas</t>
   </si>
   <si>
-    <t>Orden ascendente/descendente</t>
-  </si>
-  <si>
-    <t>Proyecto con tareas con distintas fechas y estados</t>
+    <t>Con estado en progreso</t>
+  </si>
+  <si>
+    <t>Proyecto con tareas en estado de progreso</t>
   </si>
   <si>
     <t>1. Iniciar sesión.
 2. Ingresar a “Planificación”.
-3. Ordenar por “Fecha de creación” o “Estado”.</t>
-  </si>
-  <si>
-    <t>El listado se ordena correctamente según el criterio elegido.</t>
+3. Ordenar por “Estado: Progreso”.</t>
+  </si>
+  <si>
+    <t>El listado de tareas se ordena correctamente de acuerdo a aquellas que están en estado de "Progreso".</t>
+  </si>
+  <si>
+    <t>CP15_2_V2</t>
+  </si>
+  <si>
+    <t>Con estado completado</t>
+  </si>
+  <si>
+    <t>Proyecto con tareas en estado de "completado"</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesión.
+2. Ingresar a “Planificación”.
+3. Ordenar por “Estado: Completado”.</t>
+  </si>
+  <si>
+    <t>El listado de tareas se ordena correctamente de acuerdo a aquellas que están en estado de "Completado".</t>
   </si>
   <si>
     <t>CP15_3</t>
@@ -664,7 +813,10 @@
     <t>Se muestra el mensaje “No hay tareas que coincidan con los filtros”.</t>
   </si>
   <si>
-    <t>Líder de proyecto</t>
+    <t>La pantalla de planificación se muestra vacía, sin tareas ni mensaje informativo.</t>
+  </si>
+  <si>
+    <t>El sistema no presenta mensaje de aviso cuando no existen tareas registradas. Se sugiere agregar un mensaje que indique claramente que no hay resultados.</t>
   </si>
   <si>
     <t>CP15_5</t>
@@ -682,10 +834,7 @@
     <t>Se redirige al login con mensaje “Debe iniciar sesión”.</t>
   </si>
   <si>
-    <t>Miembro</t>
-  </si>
-  <si>
-    <t>Florencia Mendez</t>
+    <t>Se obtuvo el resultado esperado: el sistema redirige correctamente a la pantalla de inicio de sesión.</t>
   </si>
   <si>
     <t>Usabilidad</t>
@@ -706,28 +855,53 @@
     <t>CP15_7_V1</t>
   </si>
   <si>
-    <t>Ordenar por fecha</t>
-  </si>
-  <si>
-    <t>Orden ascendente</t>
-  </si>
-  <si>
-    <t>1. Presionar el encabezado “Fecha Fin”.</t>
-  </si>
-  <si>
-    <t>Las tareas se ordenan ascendentemente por fecha.</t>
+    <t>Filtrar tareas por categoría</t>
+  </si>
+  <si>
+    <t>Categoría específica</t>
+  </si>
+  <si>
+    <t>Categoría: "Documentación".</t>
+  </si>
+  <si>
+    <t>1. Ingresar a la pantalla Planificación.
+ 2. Seleccionar la categoría "Documentación" en el filtro de categorías.
+ 3. Verificar que sólo se muestran tareas de esa categoría.</t>
+  </si>
+  <si>
+    <t>Se muestran únicamente las tareas pertenecientes a la categoría seleccionada.</t>
+  </si>
+  <si>
+    <t>Se obtuvo el resultado esperado: el sistema muestra solo las tareas pertenecientes a documentación.</t>
+  </si>
+  <si>
+    <t>Líder de proyecto / Miembro</t>
+  </si>
+  <si>
+    <t>Maldonado Agustina</t>
   </si>
   <si>
     <t>CP15_7_V2</t>
   </si>
   <si>
-    <t>Orden descendente</t>
-  </si>
-  <si>
-    <t>1. Volver a presionar “Fecha Fin”.</t>
-  </si>
-  <si>
-    <t>Las tareas se ordenan descendente por fecha.</t>
+    <t>Filtrar tareas por rango de fechas</t>
+  </si>
+  <si>
+    <t>Rango de fechas</t>
+  </si>
+  <si>
+    <t>Tareas con diferentes fechas; se define un rango de fechas de inicio y fin.</t>
+  </si>
+  <si>
+    <t>1. Ingresar a la pantalla Planificación.
+ 2. Establecer un rango de fechas en los filtros de fecha de inicio y fin.
+ 3. Verificar que sólo se muestran tareas cuyas fechas se encuentran dentro del rango.</t>
+  </si>
+  <si>
+    <t>La lista de tareas se actualiza mostrando sólo aquellas que cumplen con el rango de fechas definido.</t>
+  </si>
+  <si>
+    <t>Ulloa Gonzalo</t>
   </si>
   <si>
     <t>CP15_8</t>
@@ -748,32 +922,10 @@
     <t>El sistema redirige al login e impide el acceso a las tareas.</t>
   </si>
   <si>
-    <t>Usuario no autenticado</t>
-  </si>
-  <si>
     <t>Sí</t>
   </si>
   <si>
-    <t>Interfaz</t>
-  </si>
-  <si>
-    <t>CP15_9</t>
-  </si>
-  <si>
-    <t>Verificación de diseño responsivo</t>
-  </si>
-  <si>
-    <t>Distintos tamaños de pantalla</t>
-  </si>
-  <si>
-    <t>Usuario accede desde celular y desde escritorio</t>
-  </si>
-  <si>
-    <t>1. Iniciar sesión.
-2. Ingresar a “Planificación” desde distintos dispositivos.</t>
-  </si>
-  <si>
-    <t>El listado de tareas se adapta correctamente al tamaño de pantalla.</t>
+    <t>Casos de Prueba CU 16: Comentar tarea</t>
   </si>
   <si>
     <t>CP16_01_V1</t>
@@ -792,26 +944,46 @@
     <t>El sistema guarda el comentario y muestra “El comentario ha sido agregado exitosamente”.</t>
   </si>
   <si>
-    <t xml:space="preserve">El sistema guardo el comentario correctamente en la bases de datos y se muestra el comentario </t>
+    <t>El sistema guardo el comentario correctamente en la bases de datos y se muestra el mensaje en pantalla</t>
   </si>
   <si>
     <t>Miembro / Líder de Proyecto</t>
   </si>
   <si>
-    <t>CP16_01_V2</t>
-  </si>
-  <si>
-    <t>Tarea: Testing Frontend | Comentario: “Actualizar descripción del bug.”</t>
-  </si>
-  <si>
-    <t>1. Repetir el flujo con otra tarea existente. 
-2. Guardar comentario.</t>
-  </si>
-  <si>
-    <t>El sistema guarda el comentario correctamente y lo muestra en la lista.</t>
-  </si>
-  <si>
-    <t>CP16_02_V1</t>
+    <t>Modulo de Tareas</t>
+  </si>
+  <si>
+    <t>CP16_2</t>
+  </si>
+  <si>
+    <t>Cancelar comentario</t>
+  </si>
+  <si>
+    <t>El usuario cancela</t>
+  </si>
+  <si>
+    <t>Tarea: Implementar CU15: Crear tarea</t>
+  </si>
+  <si>
+    <t>1. Ingresar a la pantalla Planificación.
+2. Seleccionar “Agregar comentario” en una tarea.
+3. En la pantalla de comentarios, presionar “Cancelar”.
+4. Verificar que se regresa a la lista de tareas sin guardar el comentario.</t>
+  </si>
+  <si>
+    <t>La pantalla de comentarios se cierra y se regresa a la lista de tareas sin guardar el comentario.</t>
+  </si>
+  <si>
+    <t>La pantalla de comentarios se cerró sin guardar el comentario.</t>
+  </si>
+  <si>
+    <t>Miembro / Líder de proyecto</t>
+  </si>
+  <si>
+    <t>Escalante Guillermo</t>
+  </si>
+  <si>
+    <t>CP16_3_V1</t>
   </si>
   <si>
     <t>Comentario: vacío</t>
@@ -825,10 +997,13 @@
     <t>Se muestra el mensaje “Debe ingresar un comentario”.</t>
   </si>
   <si>
-    <t>No aparece nada</t>
-  </si>
-  <si>
-    <t>CP16_02_V2</t>
+    <t>El sistema no muestra ningún mensaje ni permite continuar. La ventana de comentario permanece abierta y no responde a la acción de guardar, por lo que no se genera retroalimentación al usuario.</t>
+  </si>
+  <si>
+    <t>Sería conveniente implementar una validación visible o mensaje de error para guiar al usuario cuando intenta guardar un comentario vacío.</t>
+  </si>
+  <si>
+    <t>CP16_3_V2</t>
   </si>
   <si>
     <t>Comentario: solo espacios (“ ”)</t>
@@ -838,39 +1013,47 @@
 2. Presionar “Aceptar”.</t>
   </si>
   <si>
-    <t>Longitud del texto</t>
-  </si>
-  <si>
-    <t>CP16_03_V1</t>
+    <t>El sistema no muestra ningún mensaje de validación. La ventana permanece abierta sin permitir avanzar ni guardar el comentario. No se informa al usuario que el campo no puede contener solo espacios.</t>
+  </si>
+  <si>
+    <t>El sistema no diferencia entre un comentario vacío y uno con solo espacios. No muestra mensaje de error y deja la interfaz sin respuesta. Se recomienda aplicar una validación adicional que elimine espacios en blanco antes de validar el contenido, mostrando el mensaje correspondiente cuando no haya texto real ingresado.</t>
+  </si>
+  <si>
+    <t>CP16_4_V1</t>
   </si>
   <si>
     <t>Valor límite</t>
   </si>
   <si>
-    <t>Comentario: 450 caracteres</t>
-  </si>
-  <si>
-    <t>1. Ingresar comentario de 450 caracteres. 
+    <t xml:space="preserve">Comentario: Estesuncomentariolargoparapruebasdesistemaquebuscaprobarlalongitudmáximadecampotipotextoen
+</t>
+  </si>
+  <si>
+    <t>1. Ingresar comentario de 100 caracteres. 
 2. Presionar “Aceptar”.</t>
   </si>
   <si>
     <t>El sistema guarda el comentario correctamente.</t>
   </si>
   <si>
-    <t>CP16_03_V2</t>
-  </si>
-  <si>
-    <t>Comentario: 520 caracteres</t>
-  </si>
-  <si>
-    <t>1. Ingresar comentario de 520 caracteres. 
+    <t>CP16_4_V2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comentario: Pruebadelongituddelcomentarioenelsistemaparaverificarsielformulariopermitealmacenartextoslargossinenviarloserróneamenteycomprobarsielcampodelabaseyelasvalidacionesdelbackendfuncionancorrectamente
+</t>
+  </si>
+  <si>
+    <t>1. Ingresar comentario de 200 caracteres. 
 2. Presionar “Aceptar”.</t>
   </si>
   <si>
     <t>Se muestra “El comentario excede la longitud permitida”.</t>
   </si>
   <si>
-    <t>CP16_04_V1</t>
+    <t>El sistema recorta el texto, queda sin respuesta al presionar “Aceptar” y no se muestra mensaje de error ni confirmación.</t>
+  </si>
+  <si>
+    <t>CP16_5</t>
   </si>
   <si>
     <t>1. Abrir ventana “Comentar”. 
@@ -878,17 +1061,50 @@
 3. Presionar “Cancelar”.</t>
   </si>
   <si>
-    <t>El sistema vuelve a la pantalla de tareas sin guardar el comentario.</t>
-  </si>
-  <si>
-    <t>CP16_05_V1</t>
-  </si>
-  <si>
-    <t>1. Ingresar comentario. 
-2. Cortar conexión y presionar “Aceptar”.</t>
-  </si>
-  <si>
-    <t>Se muestra “Error de conexión con la base de datos”.</t>
+    <t>El sistema vuelve a la pantalla de planificación de tareas sin guardar el comentario.</t>
+  </si>
+  <si>
+    <t>CP16_6</t>
+  </si>
+  <si>
+    <t>Comentario: Esto es una prueba</t>
+  </si>
+  <si>
+    <t>1. Ver la tarea comentada
+2. Presionar el icono de "borrar" el comentario</t>
+  </si>
+  <si>
+    <t>El sistema debe borrar el comentario seleccionado</t>
+  </si>
+  <si>
+    <t>Valores límite</t>
+  </si>
+  <si>
+    <t>CP16_7</t>
+  </si>
+  <si>
+    <t>Comentario con caracteres especiales</t>
+  </si>
+  <si>
+    <t>Caracteres especiales y emojis</t>
+  </si>
+  <si>
+    <t>Comentario con tildes, símbolos y emojis.</t>
+  </si>
+  <si>
+    <t>1. Ingresar a la pantalla Planificación.
+2. Seleccionar “Agregar comentario” en una tarea.
+3. Escribir un comentario que contenga caracteres especiales (ñ, é, ¡, #) y emojis y seleccionar “Aceptar”.
+4. Verificar que el comentario se guarda y se visualiza correctamente.</t>
+  </si>
+  <si>
+    <t>El comentario con caracteres especiales se almacena y visualiza correctamente.</t>
+  </si>
+  <si>
+    <t>Mendez Florencia</t>
+  </si>
+  <si>
+    <t>Casos de Prueba CU 21: Registrar tiempo manual</t>
   </si>
   <si>
     <t>Funcional</t>
@@ -898,9 +1114,6 @@
   </si>
   <si>
     <t>CP21_01_V1</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
   </si>
   <si>
     <t>Tarea: Seleccionar una. Duración: 2h 30m 0sFecha: día actual. Descripción: Ingresar descripcion</t>
@@ -920,9 +1133,6 @@
     <t>Error: una vez registrado el tiempo no vuelven a aparecer las tareas</t>
   </si>
   <si>
-    <t>Maldonado Agustina</t>
-  </si>
-  <si>
     <t>CP21_01_V2</t>
   </si>
   <si>
@@ -930,9 +1140,6 @@
   </si>
   <si>
     <t>Error corregido, se guarda el registro y las tareas aparecen.</t>
-  </si>
-  <si>
-    <t>Validación de campos</t>
   </si>
   <si>
     <t>CP21_01_V</t>
@@ -977,9 +1184,6 @@
     <t>El sistema muestra error: “No puede registrar tiempo en una fecha futura.” y no permite guardar.</t>
   </si>
   <si>
-    <t>Error: El sistema registra una fecha futura</t>
-  </si>
-  <si>
     <t>Error corregido, el sistema muestra un alerta que no se permite registrar una fecha futura</t>
   </si>
   <si>
@@ -1021,6 +1225,9 @@
     <t>El sistema rechaza el registro indicando que la tarea no puede modificarse.</t>
   </si>
   <si>
+    <t>Interfaz</t>
+  </si>
+  <si>
     <t>1. Abrir el modal.
 2.Completar campos válidos.
 3.Cerrar el modal con el botón “Cancelar”.</t>
@@ -1041,13 +1248,46 @@
   </si>
   <si>
     <t>El input de fecha no permite seleccionar días posteriores al actual.</t>
+  </si>
+  <si>
+    <t>Error: El sistema registra una fecha pasada</t>
+  </si>
+  <si>
+    <t>CP21_13</t>
+  </si>
+  <si>
+    <t>1- Abrir el modal
+2- Selecciona una tarea
+3. Ingresar una duracion y fecha valida
+4- Ingresar una descripción con un texto demasiado largo</t>
+  </si>
+  <si>
+    <t>El campo de descripción no permite una cantidad enorme de caracteres</t>
+  </si>
+  <si>
+    <t>Error: El campo de descripción permite ingresar infinitos caracteres</t>
+  </si>
+  <si>
+    <t>CP21_14</t>
+  </si>
+  <si>
+    <t>1- Abrir el modal
+2- Selecciona una tarea
+3. Ingresar una duracion y descripción valida
+4- Ingresar una fecha invalida cc/bb/2025</t>
+  </si>
+  <si>
+    <t>El sistema debe mostrar una alerta "fecha invalida"</t>
+  </si>
+  <si>
+    <t>Error: El sistema permite guardar fechas invalidas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1092,16 +1332,27 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <b/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color theme="1"/>
@@ -1155,7 +1406,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="40">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1190,31 +1441,31 @@
     <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1233,36 +1484,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1271,17 +1507,20 @@
     <xf borderId="1" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -1678,13 +1917,13 @@
     </row>
     <row r="5" ht="69.75" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>19</v>
@@ -1696,16 +1935,16 @@
         <v>21</v>
       </c>
       <c r="G5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="4" t="s">
@@ -1723,13 +1962,13 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>19</v>
@@ -1741,16 +1980,16 @@
         <v>31</v>
       </c>
       <c r="G6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>44</v>
-      </c>
       <c r="I6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="4" t="s">
@@ -1768,13 +2007,13 @@
     </row>
     <row r="7" ht="88.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>19</v>
@@ -1786,16 +2025,16 @@
         <v>21</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="J7" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="4" t="s">
@@ -1813,13 +2052,13 @@
     </row>
     <row r="8" ht="125.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>19</v>
@@ -1831,16 +2070,16 @@
         <v>31</v>
       </c>
       <c r="G8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="4" t="s">
@@ -1858,13 +2097,13 @@
     </row>
     <row r="9" ht="165.0" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>19</v>
@@ -1873,7 +2112,7 @@
         <v>30</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>57</v>
@@ -1901,9 +2140,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="165.0" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>17</v>
@@ -1920,19 +2159,19 @@
       <c r="F10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>63</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="5" t="s">
         <v>65</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="K10" s="11"/>
+      <c r="K10" s="8"/>
       <c r="L10" s="4" t="s">
         <v>25</v>
       </c>
@@ -1943,7 +2182,7 @@
         <v>27</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -1963,19 +2202,19 @@
         <v>30</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>22</v>
+        <v>56</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" s="5" t="s">
         <v>69</v>
       </c>
+      <c r="I11" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="J11" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="4" t="s">
@@ -1988,6 +2227,51 @@
         <v>27</v>
       </c>
       <c r="O11" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2010,107 +2294,72 @@
     <col customWidth="1" min="8" max="8" width="29.38"/>
     <col customWidth="1" min="9" max="9" width="31.75"/>
     <col customWidth="1" min="10" max="10" width="26.38"/>
-    <col customWidth="1" min="12" max="12" width="19.13"/>
+    <col customWidth="1" min="11" max="11" width="14.75"/>
+    <col customWidth="1" min="12" max="12" width="15.75"/>
     <col customWidth="1" min="13" max="13" width="15.0"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O2" s="12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="93.0" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" ht="63.0" customHeight="1">
+    <row r="3" ht="93.0" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>19</v>
@@ -2119,18 +2368,20 @@
         <v>20</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="13"/>
+        <v>80</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="K3" s="6"/>
       <c r="L3" s="4" t="s">
         <v>25</v>
@@ -2143,12 +2394,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="63.0" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>81</v>
@@ -2157,21 +2408,23 @@
         <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J4" s="13"/>
+      <c r="J4" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="K4" s="6"/>
       <c r="L4" s="4" t="s">
         <v>25</v>
@@ -2186,22 +2439,22 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>87</v>
@@ -2212,8 +2465,12 @@
       <c r="I5" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="6"/>
+      <c r="J5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>90</v>
+      </c>
       <c r="L5" s="4" t="s">
         <v>25</v>
       </c>
@@ -2227,10 +2484,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>91</v>
@@ -2239,22 +2496,26 @@
         <v>19</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="6"/>
+      <c r="K6" s="13" t="s">
+        <v>96</v>
+      </c>
       <c r="L6" s="4" t="s">
         <v>25</v>
       </c>
@@ -2268,34 +2529,38 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
+        <v>101</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="L7" s="4" t="s">
         <v>25</v>
       </c>
@@ -2309,34 +2574,38 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
+        <v>107</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="L8" s="4" t="s">
         <v>25</v>
       </c>
@@ -2350,34 +2619,38 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+        <v>113</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="L9" s="4" t="s">
         <v>25</v>
       </c>
@@ -2386,39 +2659,41 @@
         <v>27</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="14"/>
       <c r="L10" s="4" t="s">
         <v>25</v>
       </c>
@@ -2427,44 +2702,56 @@
         <v>27</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
+      <c r="A11" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>126</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2479,99 +2766,63 @@
     <col customWidth="1" min="4" max="4" width="10.13"/>
     <col customWidth="1" min="5" max="5" width="12.13"/>
     <col customWidth="1" min="6" max="6" width="10.25"/>
-    <col customWidth="1" min="7" max="7" width="16.0"/>
-    <col customWidth="1" min="8" max="8" width="19.5"/>
-    <col customWidth="1" min="9" max="9" width="18.25"/>
+    <col customWidth="1" min="7" max="7" width="20.25"/>
+    <col customWidth="1" min="8" max="8" width="22.13"/>
+    <col customWidth="1" min="9" max="9" width="20.75"/>
     <col customWidth="1" min="10" max="10" width="21.38"/>
     <col customWidth="1" min="13" max="13" width="16.75"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -2579,31 +2830,35 @@
         <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="18"/>
+        <v>131</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="16"/>
       <c r="L3" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>26</v>
@@ -2620,31 +2875,35 @@
         <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="18"/>
+        <v>131</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K4" s="16"/>
       <c r="L4" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>26</v>
@@ -2661,31 +2920,35 @@
         <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="K5" s="16"/>
+      <c r="L5" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>26</v>
@@ -2698,158 +2961,136 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="8"/>
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="K6" s="16"/>
       <c r="L6" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
+      <c r="N6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="15"/>
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="K7" s="8"/>
       <c r="L7" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
     </row>
     <row r="8">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="11"/>
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" s="8"/>
       <c r="L8" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2871,95 +3112,55 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -2967,38 +3168,38 @@
         <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K3" s="18"/>
+        <v>163</v>
+      </c>
+      <c r="K3" s="16"/>
       <c r="L3" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>27</v>
@@ -3012,38 +3213,38 @@
         <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K4" s="18"/>
+        <v>163</v>
+      </c>
+      <c r="K4" s="16"/>
       <c r="L4" s="4" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>27</v>
@@ -3057,38 +3258,38 @@
         <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K5" s="18"/>
+        <v>163</v>
+      </c>
+      <c r="K5" s="16"/>
       <c r="L5" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>27</v>
@@ -3099,41 +3300,41 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K6" s="18"/>
+        <v>163</v>
+      </c>
+      <c r="K6" s="16"/>
       <c r="L6" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>27</v>
@@ -3144,41 +3345,41 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K7" s="18"/>
+        <v>163</v>
+      </c>
+      <c r="K7" s="16"/>
       <c r="L7" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>27</v>
@@ -3189,41 +3390,41 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K8" s="14"/>
+        <v>163</v>
+      </c>
+      <c r="K8" s="16"/>
       <c r="L8" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>27</v>
@@ -3234,41 +3435,41 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K9" s="13"/>
+        <v>163</v>
+      </c>
+      <c r="K9" s="18"/>
       <c r="L9" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>27</v>
@@ -3279,46 +3480,94 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="K10" s="13"/>
+      <c r="K10" s="14"/>
       <c r="L10" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+        <v>164</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3330,106 +3579,69 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="14.38"/>
     <col customWidth="1" min="2" max="2" width="22.5"/>
-    <col customWidth="1" min="5" max="5" width="32.38"/>
+    <col customWidth="1" min="5" max="5" width="37.63"/>
     <col customWidth="1" min="6" max="6" width="26.88"/>
     <col customWidth="1" min="7" max="7" width="42.63"/>
     <col customWidth="1" min="8" max="8" width="49.38"/>
     <col customWidth="1" min="9" max="9" width="46.38"/>
-    <col customWidth="1" min="10" max="10" width="27.13"/>
-    <col customWidth="1" min="11" max="11" width="17.5"/>
-    <col customWidth="1" min="12" max="12" width="27.0"/>
+    <col customWidth="1" min="10" max="10" width="30.38"/>
+    <col customWidth="1" min="11" max="11" width="28.38"/>
+    <col customWidth="1" min="12" max="12" width="20.63"/>
     <col customWidth="1" min="13" max="13" width="18.38"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O2" s="19" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="25"/>
-      <c r="L2" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -3437,40 +3649,44 @@
         <v>16</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>173</v>
+      <c r="E3" s="23" t="s">
+        <v>198</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="J3" s="21"/>
+        <v>202</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>163</v>
+      </c>
       <c r="K3" s="25"/>
-      <c r="L3" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="M3" s="21"/>
+      <c r="L3" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>204</v>
+      </c>
       <c r="N3" s="21" t="s">
         <v>27</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -3478,164 +3694,176 @@
         <v>16</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>181</v>
+        <v>206</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>208</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="J4" s="21"/>
+        <v>209</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>163</v>
+      </c>
       <c r="K4" s="25"/>
-      <c r="L4" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="M4" s="21"/>
+      <c r="L4" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="M4" s="22" t="s">
+        <v>204</v>
+      </c>
       <c r="N4" s="21" t="s">
         <v>27</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>164</v>
+      <c r="A5" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>186</v>
+        <v>211</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>206</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="J5" s="22"/>
+        <v>215</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>163</v>
+      </c>
       <c r="K5" s="25"/>
-      <c r="L5" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="22" t="s">
-        <v>35</v>
+      <c r="L5" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="M5" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="21" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>164</v>
+      <c r="A6" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>196</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>194</v>
+        <v>216</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>219</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>196</v>
+        <v>220</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>221</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>9</v>
+        <v>163</v>
       </c>
       <c r="K6" s="25"/>
-      <c r="L6" s="22" t="s">
-        <v>197</v>
+      <c r="L6" s="23" t="s">
+        <v>203</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="N6" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="22" t="s">
-        <v>119</v>
+        <v>204</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="22" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>110</v>
+        <v>225</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>110</v>
+        <v>226</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="I7" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="J7" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="L7" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="J7" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="25"/>
-      <c r="L7" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="M7" s="22"/>
+      <c r="M7" s="22" t="s">
+        <v>204</v>
+      </c>
       <c r="N7" s="22" t="s">
         <v>27</v>
       </c>
@@ -3643,195 +3871,293 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" ht="21.75" customHeight="1">
-      <c r="A8" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="26" t="s">
+    <row r="8">
+      <c r="A8" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="K8" s="25"/>
+      <c r="L8" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="M8" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="J8" s="27"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="26" t="s">
+      <c r="N8" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="K9" s="25"/>
+      <c r="L9" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="M9" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="N9" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="22" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="J9" s="27"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" ht="33.75" customHeight="1">
-      <c r="A10" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>119</v>
+    <row r="10" ht="63.75" customHeight="1">
+      <c r="A10" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K10" s="25"/>
+      <c r="L10" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="M10" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="N10" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="24" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="H11" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="I11" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="J11" s="33"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="O11" s="33" t="s">
+      <c r="A11" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="K11" s="25"/>
+      <c r="L11" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="M11" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="N11" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15">
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
+    <row r="12" ht="33.75" customHeight="1">
+      <c r="A12" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="K12" s="26"/>
+      <c r="L12" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="M12" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="N12" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="O12" s="24" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+    </row>
+    <row r="18">
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
+      <c r="V18" s="28"/>
+    </row>
+    <row r="19">
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3849,446 +4175,486 @@
     <col customWidth="1" min="7" max="7" width="31.88"/>
     <col customWidth="1" min="8" max="8" width="39.63"/>
     <col customWidth="1" min="9" max="9" width="28.88"/>
-    <col customWidth="1" min="10" max="10" width="20.5"/>
+    <col customWidth="1" min="10" max="10" width="23.88"/>
+    <col customWidth="1" min="11" max="11" width="23.13"/>
     <col customWidth="1" min="12" max="12" width="22.75"/>
     <col customWidth="1" min="13" max="13" width="17.38"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="36">
+      <c r="D2" s="30">
         <v>0.0</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E2" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="36" t="s">
+      <c r="K2" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="36" t="s">
+      <c r="L2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="36" t="s">
+      <c r="M2" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="36" t="s">
+      <c r="N2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="36" t="s">
+      <c r="O2" s="30" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="37" t="s">
+    <row r="3">
+      <c r="A3" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="37" t="s">
+      <c r="B3" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>232</v>
-      </c>
-      <c r="K2" s="38"/>
-      <c r="L2" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="37" t="s">
+      <c r="G3" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="K3" s="33"/>
+      <c r="L3" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="32" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="37" t="s">
+    <row r="4">
+      <c r="A4" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="37" t="s">
+      <c r="B4" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="K4" s="33"/>
+      <c r="L4" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="M5" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="N5" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="H3" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="I3" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="M3" s="37"/>
-      <c r="N3" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="37" t="s">
+      <c r="G6" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="K6" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="L6" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="M6" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="N6" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="32" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4" s="37" t="s">
+    <row r="7">
+      <c r="A7" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="F7" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>240</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="K4" s="38"/>
-      <c r="L4" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="37" t="s">
+      <c r="G7" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="33"/>
+      <c r="L7" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="M7" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="32" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="37" t="s">
+    <row r="8">
+      <c r="A8" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="F8" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="37" t="s">
-        <v>244</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="I5" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="K5" s="38"/>
-      <c r="L5" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="37" t="s">
+      <c r="G8" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="K8" s="33"/>
+      <c r="L8" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="M8" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="32" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="37" t="s">
+    <row r="9">
+      <c r="A9" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>250</v>
-      </c>
-      <c r="I6" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="37" t="s">
+      <c r="G9" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="33"/>
+      <c r="L9" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="M9" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="N9" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>308</v>
+      </c>
+      <c r="I10" s="36" t="s">
+        <v>309</v>
+      </c>
+      <c r="J10" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="37"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="G11" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>316</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="37"/>
+      <c r="L11" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="M11" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="N11" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="34" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="39" t="s">
-        <v>248</v>
-      </c>
-      <c r="F7" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="39" t="s">
-        <v>253</v>
-      </c>
-      <c r="H7" s="39" t="s">
-        <v>254</v>
-      </c>
-      <c r="I7" s="39" t="s">
-        <v>255</v>
-      </c>
-      <c r="J7" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="K7" s="40"/>
-      <c r="L7" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="39" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>256</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="H8" s="39" t="s">
-        <v>257</v>
-      </c>
-      <c r="I8" s="39" t="s">
-        <v>258</v>
-      </c>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="I9" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="J9" s="41"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="29" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
+    <row r="18">
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4301,562 +4667,587 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="14.13"/>
-    <col customWidth="1" min="7" max="7" width="15.0"/>
+    <col customWidth="1" min="4" max="4" width="10.0"/>
+    <col customWidth="1" min="6" max="6" width="0.38"/>
+    <col customWidth="1" min="7" max="7" width="17.63"/>
     <col customWidth="1" min="8" max="8" width="26.25"/>
     <col customWidth="1" min="9" max="9" width="23.25"/>
-    <col customWidth="1" min="10" max="10" width="26.0"/>
+    <col customWidth="1" min="10" max="10" width="23.0"/>
     <col customWidth="1" min="13" max="13" width="15.75"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="43" t="s">
-        <v>262</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E2" s="43" t="s">
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="43"/>
-      <c r="G2" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="J2" s="43" t="s">
-        <v>269</v>
-      </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M2" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N2" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="43" t="s">
+      <c r="F3" s="39"/>
+      <c r="G3" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="K3" s="16"/>
+      <c r="L3" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="43" t="s">
-        <v>262</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C3" s="37" t="s">
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="39"/>
+      <c r="G4" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="K4" s="16"/>
+      <c r="L4" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D3" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E3" s="43" t="s">
+      <c r="M4" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="16"/>
+      <c r="L5" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="16"/>
+      <c r="L6" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="K7" s="16"/>
+      <c r="L7" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="39"/>
+      <c r="G8" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="16"/>
+      <c r="L8" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="43"/>
-      <c r="G3" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="J3" s="43" t="s">
-        <v>273</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M3" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="43" t="s">
+      <c r="F9" s="39"/>
+      <c r="G9" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="16"/>
+      <c r="L9" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="39"/>
+      <c r="G10" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="18"/>
+      <c r="L10" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="43" t="s">
-        <v>274</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E4" s="43" t="s">
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M4" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N4" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="43" t="s">
+      <c r="F11" s="39"/>
+      <c r="G11" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="43" t="s">
-        <v>274</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E5" s="43" t="s">
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="43"/>
-      <c r="G5" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M5" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N5" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="43" t="s">
+      <c r="F13" s="17"/>
+      <c r="G13" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="43" t="s">
-        <v>274</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="J6" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M6" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N6" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="43" t="s">
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="17"/>
+      <c r="G14" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="K14" s="18"/>
+      <c r="L14" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="43" t="s">
-        <v>274</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="J7" s="43" t="s">
-        <v>286</v>
-      </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M7" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N7" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="s">
-        <v>274</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M8" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N8" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M9" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N9" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="s">
-        <v>262</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M10" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N10" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O10" s="43" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E11" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M11" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N11" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O11" s="43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="E12" s="43" t="s">
-        <v>298</v>
-      </c>
-      <c r="F12" s="43"/>
-      <c r="G12" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="M12" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="N12" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="O12" s="43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15"/>
-      <c r="B13" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15"/>
-      <c r="B14" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Etapa Construcción - Iteración 2/Diseño - Especificación de CUs ／ Casos de prueba/Casos de prueba 2° tanda de Casos de Uso- Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 2/Diseño - Especificación de CUs ／ Casos de prueba/Casos de prueba 2° tanda de Casos de Uso- Kairos - NexTech.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="CU07 Crear Etapa" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="CU08 Crear Iteración" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="CU13 Asignar Dependencia" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="CU14 Modificar Estado de Tarea" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="CU15 Visualizar Tarea" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="CU16 Comentar Tarea" sheetId="6" r:id="rId9"/>
-    <sheet state="visible" name="CU21 Registrar Tiempo Manual" sheetId="7" r:id="rId10"/>
+    <sheet state="visible" name="CU07 Crear Etapa" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="CU08 Crear Iteración" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="CU13 Asignar Dependencia" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="CU14 Modificar Estado de Tarea" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="CU15 Visualizar Tarea" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="CU16 Comentar Tarea" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="CU21 Registrar Tiempo Manual" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -1561,6 +1561,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
